--- a/deaba/plantilla/Plantilla_DEAba_tipo2.xlsx
+++ b/deaba/plantilla/Plantilla_DEAba_tipo2.xlsx
@@ -496,7 +496,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Rellena la columna Valor. «tipo» es 1 (interpretar datos de expresión diferencial) o 2 (diseñar el experimento).</t>
+          <t>Rellena la columna Valor (y, si quieres la actividad también en inglés, «Valor (en)» y las columnas «Nombre (en)»; si se dejan vacías, se muestra el español). «tipo» es 1 (interpretar datos de expresión diferencial) o 2 (diseñar el experimento).</t>
         </is>
       </c>
     </row>
@@ -642,11 +642,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="120" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -660,6 +661,11 @@
           <t>Valor</t>
         </is>
       </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Valor (en)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -668,6 +674,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr"/>
+      <c r="C2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -678,6 +685,7 @@
       <c r="B3" s="5" t="n">
         <v>2</v>
       </c>
+      <c r="C3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -686,6 +694,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -694,6 +703,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -702,6 +712,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -710,6 +721,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -718,6 +730,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -726,6 +739,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -734,6 +748,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -742,6 +757,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -754,6 +770,7 @@
           <t>3;3;4</t>
         </is>
       </c>
+      <c r="C12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -762,6 +779,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr"/>
+      <c r="C13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -770,6 +788,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr"/>
+      <c r="C14" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -782,13 +801,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -804,10 +824,15 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
+          <t>Nombre (en)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
           <t>Comentario (guía)</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Papel</t>
         </is>
@@ -815,7 +840,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"referencia_1,referencia_2,valida,debil"</formula1>
     </dataValidation>
   </dataValidations>
@@ -829,21 +854,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -864,45 +890,50 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
+          <t>Nombre (en)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
           <t>Papel</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Reacción</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Rutas</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Compartimento</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Por qué</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Palabras clave</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Nivel: c1</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Nivel: c2</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Nivel: c3</t>
         </is>
@@ -913,7 +944,7 @@
     <dataValidation sqref="B2:B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"enzima,metabolito"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"clave,apoyo,distractor"</formula1>
     </dataValidation>
   </dataValidations>

--- a/deaba/plantilla/Plantilla_DEAba_tipo2.xlsx
+++ b/deaba/plantilla/Plantilla_DEAba_tipo2.xlsx
@@ -484,33 +484,33 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Las columnas «(en)» son opcionales: si están vacías, se muestra el español.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Hoja «Actividad»</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Rellena la columna Valor (y, si quieres la actividad también en inglés, «Valor (en)» y las columnas «Nombre (en)»; si se dejan vacías, se muestra el español). «tipo» es 1 (interpretar datos de expresión diferencial) o 2 (diseñar el experimento).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>«id» sigue el formato condición_tipo_nivel (por ejemplo, diabetes_t1_medium); nivel = low, medium o high.</t>
+          <t>«tipo» es 1 (interpretar datos de expresión diferencial) o 2 (diseñar el experimento). «id» sigue el formato condición_tipo_nivel (p. ej., diabetes_t1_medium); nivel = low, medium o high.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>«puntos» son los de las tres tareas, separados por «;». Tipo 1: reacciones; rutas; diagnóstico (3;3;4). Tipo 2: condiciones; enzimas, reacciones y rutas; fold change (3;3;4).</t>
+          <t>«puntos»: los de las tres tareas, separados por «;». Tipo 1: reacciones; rutas; diagnóstico (3;3;4). Tipo 2: condiciones; enzimas, reacciones y rutas; fold change (3;3;4).</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Las filas marcadas en amarillo («objetivo», «nivel_texto») solo aparecen en la guía del profesor.</t>
+          <t>Las filas en amarillo («objetivo», «nivel_texto») solo aparecen en la guía del profesor.</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Id, Tipo (enzima o metabolito), Nombre y FC son lo que ven los grupos. Un FC negativo significa −1/valor (como en clase).</t>
+          <t>Id, Tipo (enzima o metabolito), Nombre y FC son lo que ven los grupos. Un FC negativo significa −1/valor.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Las columnas amarillas son la clave para la guía y el panel: reacción, rutas (identificadores de la hoja «Rutas», separados por «;»), compartimento, por qué cambia y palabras clave de la reacción (separadas por «;»).</t>
+          <t>Las columnas amarillas son la clave: reacción, rutas (identificadores de la hoja «Rutas», separados por «;»), compartimento, por qué cambia y palabras clave de la reacción (separadas por «;»).</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Las columnas «Nivel: …» son la abundancia relativa en cada condición; al «ejecutar el experimento», el fold change se calcula como nivel cond1 / nivel cond2. 0 = no detectado.</t>
+          <t>Las columnas «Nivel: …» son la abundancia relativa en cada condición; al «ejecutar el experimento», el FC se calcula como nivel cond1 / nivel cond2. 0 = no detectado.</t>
         </is>
       </c>
     </row>
@@ -613,14 +613,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Lo que el panel busca en las justificaciones (ayuda para el profesor, no corrige). Términos: alternativas separadas por «;» (basta con que aparezca una). Para que una alternativa exija dos palabras a la vez, únelas con «+»: «malonil + carnitina; malonil + cat» se cumple si aparecen «malonil» y «carnitina», o «malonil» y «cat».</t>
+          <t>Lo que el panel busca en las respuestas (ayuda para el profesor, no corrige). Términos: alternativas separadas por «;» (basta con que aparezca una). Para que una alternativa exija dos palabras a la vez, únelas con «+»: «malonil + carnitina; malonil + cat».</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Se ignoran tildes y mayúsculas; «*» al final de una palabra admite cualquier terminación (cetonic* → cetónico, cetónicos). Si va precedido de «no», «sin», «ni»… se marca como negado.</t>
+          <t>Se ignoran tildes y mayúsculas; «*» al final de una palabra admite cualquier terminación (cetonic* → cetónico, cetónicos). Si va precedido de «no», «sin», «ni»… se marca como negado. Incluye también los términos en inglés si la actividad se usa en inglés.</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
+      <c r="C13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
+      <c r="C14" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -801,14 +801,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -834,13 +835,18 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>Comentario (en)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>Papel</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"referencia_1,referencia_2,valida,debil"</formula1>
     </dataValidation>
   </dataValidations>
@@ -854,22 +860,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="56" customWidth="1" min="11" max="11"/>
+    <col width="56" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,35 +914,50 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
+          <t>Reacción (en)</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>Rutas</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Compartimento</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Compartimento (en)</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Por qué</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Por qué (en)</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Palabras clave</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Nivel: c1</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Nivel: c2</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Nivel: c3</t>
         </is>
@@ -958,11 +982,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="130" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -976,10 +1001,15 @@
           <t>Texto</t>
         </is>
       </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Texto (en)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A2:A300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"diagnostico,pistas,razonamiento,alternativas,errores,plenario,referencias,notas"</formula1>
     </dataValidation>
   </dataValidations>
@@ -993,13 +1023,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1015,10 +1046,15 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
+          <t>Etiqueta (en)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
           <t>Términos</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
@@ -1026,7 +1062,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"esperado,alternativo,error"</formula1>
     </dataValidation>
   </dataValidations>

--- a/deaba/plantilla/Plantilla_DEAba_tipo2.xlsx
+++ b/deaba/plantilla/Plantilla_DEAba_tipo2.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -529,103 +529,110 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>«doi» es opcional: si la actividad tiene su propio DOI (p. ej., en Zenodo, 10.5281/zenodo.1234567), la guía y la versión en papel muestran cómo citarla.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Hoja «Moléculas» (solo tipo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Id, Tipo (enzima o metabolito), Nombre y FC son lo que ven los grupos. Un FC negativo significa −1/valor.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>Id, Tipo (enzima o metabolito), Nombre y FC son lo que ven los grupos. Un FC negativo significa −1/valor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>Las columnas amarillas son la clave: reacción, rutas (identificadores de la hoja «Rutas», separados por «;»), compartimento, por qué cambia y palabras clave de la reacción (separadas por «;»).</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-    </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Hojas «Condiciones» y «Marcadores» (solo tipo 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Condiciones: las situaciones entre las que pueden elegir los grupos. Papel: referencia_1 y referencia_2 (la comparación recomendada), valida o debil.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Marcadores: el catálogo que verán los grupos (incluye distractores, en orden alfabético). Papel: clave, apoyo o distractor.</t>
+          <t>Condiciones: las situaciones entre las que pueden elegir los grupos. Papel: referencia_1 y referencia_2 (la comparación recomendada), valida o debil.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>Marcadores: el catálogo que verán los grupos (incluye distractores, en orden alfabético). Papel: clave, apoyo o distractor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>Las columnas «Nivel: …» son la abundancia relativa en cada condición; al «ejecutar el experimento», el FC se calcula como nivel cond1 / nivel cond2. 0 = no detectado.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-    </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Hoja «Guía»</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Una fila por idea. Secciones: diagnostico, pistas, razonamiento, alternativas, errores, plenario, referencias, notas.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-    </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Hoja «Conceptos»</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Lo que el panel busca en las respuestas (ayuda para el profesor, no corrige). Términos: alternativas separadas por «;» (basta con que aparezca una). Para que una alternativa exija dos palabras a la vez, únelas con «+»: «malonil + carnitina; malonil + cat».</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Se ignoran tildes y mayúsculas; «*» al final de una palabra admite cualquier terminación (cetonic* → cetónico, cetónicos). Si va precedido de «no», «sin», «ni»… se marca como negado. Incluye también los términos en inglés si la actividad se usa en inglés.</t>
+          <t>Lo que el panel busca en las respuestas (ayuda para el profesor, no corrige). Términos: alternativas separadas por «;» (basta con que aparezca una). Para que una alternativa exija dos palabras a la vez, únelas con «+»: «malonil + carnitina; malonil + cat».</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Se ignoran tildes y mayúsculas; «*» al final de una palabra admite cualquier terminación (cetonic* → cetónico, cetónicos). Si va precedido de «no», «sin», «ni»… se marca como negado. Incluye también los términos en inglés si la actividad se usa en inglés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Tipo: esperado, alternativo o error.</t>
         </is>
@@ -642,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -726,16 +733,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>contexto</t>
+          <t>doi</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mision</t>
+          <t>contexto</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr"/>
@@ -744,16 +751,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>n_enzimas</t>
+          <t>mision</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
+      <c r="C10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>n_metabolitos</t>
+          <t>n_enzimas</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr"/>
@@ -762,33 +769,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>n_metabolitos</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>puntos</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>3;3;4</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>objetivo</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr"/>
-      <c r="C13" s="7" t="inlineStr"/>
+      <c r="C13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>nivel_texto</t>
+          <t>objetivo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr"/>
       <c r="C14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>nivel_texto</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
